--- a/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
+++ b/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_FRAMEWORK\AutomationFrameworkSelenium\src\test\resources\testdataCRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9EEB5B-8318-401E-AB57-AE20F46AC1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0F671-25F0-45D0-B733-94EF8F3BB489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{7A35AAC3-973C-4AA0-816A-DECEFD0ED1D8}"/>
   </bookViews>
@@ -115,9 +115,6 @@
     <t>eCommerce</t>
   </si>
   <si>
-    <t>Anh Tester Client 0108A3</t>
-  </si>
-  <si>
     <t>Address 1</t>
   </si>
   <si>
@@ -139,21 +136,12 @@
     <t>admin@example.com</t>
   </si>
   <si>
-    <t>client@example.com</t>
-  </si>
-  <si>
     <t>T+wyT5u9cOelDJbBWNgxLw==</t>
   </si>
   <si>
     <t>Admin Example</t>
   </si>
   <si>
-    <t>Anh Tester Client 1812A1</t>
-  </si>
-  <si>
-    <t>Anh Tester Client 1812A2</t>
-  </si>
-  <si>
     <t>VN</t>
   </si>
   <si>
@@ -167,6 +155,18 @@
   </si>
   <si>
     <t>TV</t>
+  </si>
+  <si>
+    <t>customer@example.com</t>
+  </si>
+  <si>
+    <t>Anh Tester Client 2602A1</t>
+  </si>
+  <si>
+    <t>Anh Tester Client 2602A2</t>
+  </si>
+  <si>
+    <t>Anh Tester Client 2602A3</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="20.09765625" style="10" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.3984375" style="10" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="41.19921875" style="10" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="21.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="23.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
@@ -698,10 +698,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="11"/>
@@ -714,10 +714,10 @@
         <v>22</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -741,7 +741,7 @@
   <sheetFormatPr defaultColWidth="18.19921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.8984375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.69921875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="33.796875" style="2" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="21.8984375" style="2" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="11.69921875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
@@ -806,25 +806,25 @@
         <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G2" s="3">
         <v>1001</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I2" s="3">
         <v>123456</v>
@@ -847,25 +847,25 @@
         <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3">
         <v>1002</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3">
         <v>123456</v>
@@ -888,25 +888,25 @@
         <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3">
         <v>1003</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3">
         <v>123456</v>
